--- a/public/translation.xlsx
+++ b/public/translation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2293b72959587e28/PAYT_ANALYSIS/model/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="8_{6AF8692F-890D-1B44-9F64-197BE6160813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F6A9A99-F55E-7A4C-B67E-A570C14EBBEB}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="8_{6AF8692F-890D-1B44-9F64-197BE6160813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E71E475-E12D-8E4F-BAC4-DC8AE45E9391}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="12540" windowWidth="31520" windowHeight="14460" xr2:uid="{8B6CA0FD-2112-BC45-8C8C-A886CDF59FA5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="224">
   <si>
     <t>key</t>
   </si>
@@ -50,478 +50,739 @@
     <t>intro</t>
   </si>
   <si>
+    <t>## Parameter setup</t>
+  </si>
+  <si>
+    <t>### General assumptions and policy changes</t>
+  </si>
+  <si>
+    <t>**Annual rate of growth for fee collection (new construction, etc.) in %**</t>
+  </si>
+  <si>
+    <t>**Make OLO handle waste collection from local waste collection yards**</t>
+  </si>
+  <si>
+    <t>**Share of individual bins that are filled to capacity in %**</t>
+  </si>
+  <si>
+    <t>**Behavioral scenario**</t>
+  </si>
+  <si>
+    <t>**Assumption for how much more expensive OLO is compared to local yards (multiplier)**</t>
+  </si>
+  <si>
+    <t>**2024 value for other expenses covered by waste fees**</t>
+  </si>
+  <si>
+    <t>**Organic waste pickup frequency**</t>
+  </si>
+  <si>
+    <t>**Upload new OLO expenditure**</t>
+  </si>
+  <si>
+    <t>### Individual homes (simple setup)</t>
+  </si>
+  <si>
+    <t>**1 Increase in standard fee in %**</t>
+  </si>
+  <si>
+    <t>**2 Force a maximum 14d interval for individual homes**</t>
+  </si>
+  <si>
+    <t>**3 Number of years to forecast**</t>
+  </si>
+  <si>
+    <t>### Individual homes (complex setup)</t>
+  </si>
+  <si>
+    <t>In this table, you can add multiple rows as steps in gradual fee increase / change</t>
+  </si>
+  <si>
+    <t>### Coops/businesses (simple setup)</t>
+  </si>
+  <si>
+    <t>**2 Number of people per 1110l bin**</t>
+  </si>
+  <si>
+    <t>### Coops/businesses (complex setup)</t>
+  </si>
+  <si>
+    <t>## Illustrations of monthly fee rises for current setup</t>
+  </si>
+  <si>
+    <t>### Household modelling</t>
+  </si>
+  <si>
+    <t>#### Simple setup</t>
+  </si>
+  <si>
+    <t>1 Individual home | Weekly pickup | 120L</t>
+  </si>
+  <si>
+    <t>€ monthly increase</t>
+  </si>
+  <si>
+    <t>2 Individual home | 2x monthly pickup | 120L</t>
+  </si>
+  <si>
+    <t>3 Block of flats | 2x weekly pickup | 1100L | 45 people per bin</t>
+  </si>
+  <si>
+    <t>4 Block of flats | 3x weekly pickup | 1100L | 60 people per bin</t>
+  </si>
+  <si>
+    <t>#### Stepped setup</t>
+  </si>
+  <si>
+    <t>### Per-bin modelling</t>
+  </si>
+  <si>
+    <t>5 120L | 2x monthly pickup</t>
+  </si>
+  <si>
+    <t>6 240L | 2x monthly pickup</t>
+  </si>
+  <si>
+    <t>7 1100L | 2x weekly pickup</t>
+  </si>
+  <si>
+    <t>## Total results for all behavioral scenarios</t>
+  </si>
+  <si>
+    <t>Total fee forecast per behavioral scenario (Simple | Organic Pickup:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total fee forecast per behavioral scenario (Stepped | Organic Pickup: </t>
+  </si>
+  <si>
+    <t>### Data from total results chart to export</t>
+  </si>
+  <si>
+    <t>You can press *Download* under the table to export your data to CSV to be used in Excel</t>
+  </si>
+  <si>
+    <t>Charts can be saved by clicking the ... button in the corner of the chart as an image</t>
+  </si>
+  <si>
+    <t>## Simulation results (Fees)</t>
+  </si>
+  <si>
+    <t>Below you can see the total results for the current simulation setup for fees in EUR.</t>
+  </si>
+  <si>
+    <t>The table shows fees before change implementation, first year after implementation and in the last projected period.</t>
+  </si>
+  <si>
+    <t>Then the following charts show a detailed evolution over time of fee collection and the number of bins.</t>
+  </si>
+  <si>
+    <t>## Parametre modelu</t>
+  </si>
+  <si>
+    <t>### Všeobecné predpoklady a zmeny politík</t>
+  </si>
+  <si>
+    <t>**Ročné tempo rastu výnosov z poplatku (nová výstavba, atď.) v %**</t>
+  </si>
+  <si>
+    <t>**Prevezme OLO odvoz odpadu z miestnych zberných dvorov?**</t>
+  </si>
+  <si>
+    <t>**Podiel individuálnych nádob, ktoré sú plné, v %**</t>
+  </si>
+  <si>
+    <t>**Scenáre správania**</t>
+  </si>
+  <si>
+    <t>**Predpoklad rozdielu v nákladoch medzi OLO a miestnych zberných dvorov (násobok)**</t>
+  </si>
+  <si>
+    <t>**Hodnota pre ostatné náklady, hradené z poplatku (pre rok 2024)**</t>
+  </si>
+  <si>
+    <t>**Frekvencia zvozu kuchynského odpadu**</t>
+  </si>
+  <si>
+    <t>**Nahrať nové náklady OLO**</t>
+  </si>
+  <si>
+    <t>### IBV (jednoduchý model)</t>
+  </si>
+  <si>
+    <t>**1 Zvýšenie základného poplatku o %**</t>
+  </si>
+  <si>
+    <t>**2 Maximálna frekvencia 2x mesiac**</t>
+  </si>
+  <si>
+    <t>**3 Počet rokov prognózy**</t>
+  </si>
+  <si>
+    <t>### IBV (komplexný model)</t>
+  </si>
+  <si>
+    <t>V tejto tabuľke môžete pridávať riadky ako kroky v postupných zmenách poplatkov</t>
+  </si>
+  <si>
+    <t>### BD a PO (jednoduchý model)</t>
+  </si>
+  <si>
+    <t>**2 Počet obyvateľov na 1 110l nádobu**</t>
+  </si>
+  <si>
+    <t>### BD a PO (komplexný model)</t>
+  </si>
+  <si>
+    <t>## Príklady mesačných nárastov poplatok pre aktuálne nastavený model</t>
+  </si>
+  <si>
+    <t>### Domácnosti</t>
+  </si>
+  <si>
+    <t>#### Jednoduchý model</t>
+  </si>
+  <si>
+    <t>1 IBV | Týždenný zvoz | 120l</t>
+  </si>
+  <si>
+    <t>€ mesačný nárast</t>
+  </si>
+  <si>
+    <t>2 IBV | Zvoz 2x mesačne | 120l</t>
+  </si>
+  <si>
+    <t>3 Bytové domy | Zvoz 2x týždenne | 1100l | 45 ľudí na nádobu | 2 ľudia na domácnosť</t>
+  </si>
+  <si>
+    <t>4 Bytové domy | Zvoz 3x týždenne | 1100l | 60 ľudí na nádobu | 2 ľudia na domácnosť</t>
+  </si>
+  <si>
+    <t>#### Komplexný model</t>
+  </si>
+  <si>
+    <t>### Nádoby</t>
+  </si>
+  <si>
+    <t>5 120l | Zvoz 2x mesačne</t>
+  </si>
+  <si>
+    <t>6 240l | Zvoz 2x mesačne</t>
+  </si>
+  <si>
+    <t>7 1100l | Zvoz 2x týždenne</t>
+  </si>
+  <si>
+    <t>Celkový odhad výnosov z poplatku pre každý scenár (Jednoduchý model | Kuchynský odpad:</t>
+  </si>
+  <si>
+    <t>Celkový odhad výnosov z poplatku pre každý scenár (Komplexný model | Kuchynský odpad:</t>
+  </si>
+  <si>
+    <t>## Celkový výsledky pre všetky scenáre správania</t>
+  </si>
+  <si>
+    <t>### Dáta z grafu na export</t>
+  </si>
+  <si>
+    <t>Stlačením tlačidla *Download* pod tabuľkou exportujete dáta do CSV formátu, ktorý je možné použiť v Exceli</t>
+  </si>
+  <si>
+    <t>Grafy môžu byť uložené stlačením tlačidla ... v rohu grafu ako obrázok</t>
+  </si>
+  <si>
+    <t>Exportované dáta obsahujú aj zhrnutie použitých predpokladov</t>
+  </si>
+  <si>
+    <t>Exported data contain a summary of used assumptions</t>
+  </si>
+  <si>
+    <t>## Výsledky simulácie (výnos z poplatku)</t>
+  </si>
+  <si>
+    <t>Nižšie môžete vidieť celkové výsledky pre aktuálne nastavenie modelu pre výnosy z poplatku v EUR.</t>
+  </si>
+  <si>
+    <t>Tabuľka ukazuje výnosy pred zmenu, prvý rok po zmene a v poslednom roku prognózovaného obdobia.</t>
+  </si>
+  <si>
+    <t>Následne, detailné grafy ukazujú vývoj výnosov a počtu nádob v čase.</t>
+  </si>
+  <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>p3</t>
+  </si>
+  <si>
+    <t>p4</t>
+  </si>
+  <si>
+    <t>p5</t>
+  </si>
+  <si>
+    <t>p6</t>
+  </si>
+  <si>
+    <t>p7</t>
+  </si>
+  <si>
+    <t>p8</t>
+  </si>
+  <si>
+    <t>p9</t>
+  </si>
+  <si>
+    <t>p10</t>
+  </si>
+  <si>
+    <t>s1</t>
+  </si>
+  <si>
+    <t>s2</t>
+  </si>
+  <si>
+    <t>s3</t>
+  </si>
+  <si>
+    <t>s4</t>
+  </si>
+  <si>
+    <t>s5</t>
+  </si>
+  <si>
+    <t>s6</t>
+  </si>
+  <si>
+    <t>s7</t>
+  </si>
+  <si>
+    <t>s8</t>
+  </si>
+  <si>
+    <t>s9</t>
+  </si>
+  <si>
+    <t>s10</t>
+  </si>
+  <si>
+    <t>s11</t>
+  </si>
+  <si>
+    <t>e1</t>
+  </si>
+  <si>
+    <t>e2</t>
+  </si>
+  <si>
+    <t>e3</t>
+  </si>
+  <si>
+    <t>e4</t>
+  </si>
+  <si>
+    <t>e5</t>
+  </si>
+  <si>
+    <t>e6</t>
+  </si>
+  <si>
+    <t>e7</t>
+  </si>
+  <si>
+    <t>e8</t>
+  </si>
+  <si>
+    <t>e9</t>
+  </si>
+  <si>
+    <t>e10</t>
+  </si>
+  <si>
+    <t>e11</t>
+  </si>
+  <si>
+    <t>e12</t>
+  </si>
+  <si>
+    <t>e13</t>
+  </si>
+  <si>
+    <t>l1</t>
+  </si>
+  <si>
+    <t>l2</t>
+  </si>
+  <si>
+    <t>r1</t>
+  </si>
+  <si>
+    <t>r2</t>
+  </si>
+  <si>
+    <t>r3</t>
+  </si>
+  <si>
+    <t>r4</t>
+  </si>
+  <si>
+    <t>r5</t>
+  </si>
+  <si>
+    <t>r6</t>
+  </si>
+  <si>
+    <t>r7</t>
+  </si>
+  <si>
+    <t>r8</t>
+  </si>
+  <si>
+    <t>r9</t>
+  </si>
+  <si>
+    <t>ex1</t>
+  </si>
+  <si>
+    <t>-- POUZITE PREDPOKLADY --</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -- USED ASSUMPTIONS --</t>
+  </si>
+  <si>
+    <t>ex2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Zmeny sadzieb pre jednoduchy model </t>
+  </si>
+  <si>
+    <t># Fee changes for the simple model</t>
+  </si>
+  <si>
+    <t>ex3</t>
+  </si>
+  <si>
+    <t>## IBV:</t>
+  </si>
+  <si>
+    <t>## Individual households:</t>
+  </si>
+  <si>
+    <t>ex4</t>
+  </si>
+  <si>
+    <t>Bez tyzdenneho zvozu</t>
+  </si>
+  <si>
+    <t>Without weekly pickup</t>
+  </si>
+  <si>
+    <t>ex5</t>
+  </si>
+  <si>
+    <t>Tyzdenny zvoz</t>
+  </si>
+  <si>
+    <t>Weekly pickup</t>
+  </si>
+  <si>
+    <t>ex6</t>
+  </si>
+  <si>
+    <t>## PO/BD:</t>
+  </si>
+  <si>
+    <t>## Coops/businesses</t>
+  </si>
+  <si>
+    <t>ex7</t>
+  </si>
+  <si>
+    <t>ludi na nadobu</t>
+  </si>
+  <si>
+    <t>people per bin</t>
+  </si>
+  <si>
+    <t>ex8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Zmeny sadzieb pre krokovy model </t>
+  </si>
+  <si>
+    <t># Fee changes for the stepped model</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Predpoklady pre tieto vysledky: </t>
+  </si>
+  <si>
+    <t>ex9</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Assumptions for these results: </t>
+  </si>
+  <si>
+    <t>## Scenar spravania ludi:</t>
+  </si>
+  <si>
+    <t>ex10</t>
+  </si>
+  <si>
+    <t>## Behavioral scenario:</t>
+  </si>
+  <si>
+    <t>## Frekvencia odvozu kuchynskeho odpadu:</t>
+  </si>
+  <si>
+    <t>## OLO prebera:</t>
+  </si>
+  <si>
+    <t>## Tempo rastu vynosov:</t>
+  </si>
+  <si>
+    <t>## Pocet nadob, ktore su plne:</t>
+  </si>
+  <si>
+    <t>## O kolko je OLO drahsie pri zbernych dvoroch:</t>
+  </si>
+  <si>
+    <t>## Ostatne naklady spojene s odpadom:</t>
+  </si>
+  <si>
+    <t>ex11</t>
+  </si>
+  <si>
+    <t>ex12</t>
+  </si>
+  <si>
+    <t>ex13</t>
+  </si>
+  <si>
+    <t>ex14</t>
+  </si>
+  <si>
+    <t>ex15</t>
+  </si>
+  <si>
+    <t>ex16</t>
+  </si>
+  <si>
+    <t>## Organic waste pickup frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">## OLO takes over: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">## Revenue growth rate: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">## Share of bins that are full: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">## OLO cost multiplier over local yards: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">## Other expenditures related to waste collection: </t>
+  </si>
+  <si>
+    <t>d1</t>
+  </si>
+  <si>
+    <t>0 Nie</t>
+  </si>
+  <si>
+    <t>1 Iba riadne zberné dvory</t>
+  </si>
+  <si>
+    <t>2 Všetky zberné dvory a miesta</t>
+  </si>
+  <si>
+    <t>1 Bez zmeny správania</t>
+  </si>
+  <si>
+    <t>2 Štandardná odozva</t>
+  </si>
+  <si>
+    <t>3 Výrazná odozva</t>
+  </si>
+  <si>
+    <t>Súčasná frekvencia</t>
+  </si>
+  <si>
+    <t>2x/týždeň</t>
+  </si>
+  <si>
+    <t>1x/týždeň</t>
+  </si>
+  <si>
+    <t>d2</t>
+  </si>
+  <si>
+    <t>d3</t>
+  </si>
+  <si>
+    <t>d4</t>
+  </si>
+  <si>
+    <t>d5</t>
+  </si>
+  <si>
+    <t>d6</t>
+  </si>
+  <si>
+    <t>d7</t>
+  </si>
+  <si>
+    <t>d8</t>
+  </si>
+  <si>
+    <t>d9</t>
+  </si>
+  <si>
+    <t>0 None</t>
+  </si>
+  <si>
+    <t>1 Only full waste yards</t>
+  </si>
+  <si>
+    <t>2 All waste yards and points</t>
+  </si>
+  <si>
+    <t>1 No behavioral change</t>
+  </si>
+  <si>
+    <t>2 Standard response</t>
+  </si>
+  <si>
+    <t>3 Strong response</t>
+  </si>
+  <si>
+    <t>Current schedule</t>
+  </si>
+  <si>
+    <t>Twice a week</t>
+  </si>
+  <si>
+    <t>Once a week</t>
+  </si>
+  <si>
+    <t>sc1</t>
+  </si>
+  <si>
+    <t>Komplexný model</t>
+  </si>
+  <si>
+    <t>Stepped model</t>
+  </si>
+  <si>
+    <t>sc2</t>
+  </si>
+  <si>
+    <t>Jednoduchý model</t>
+  </si>
+  <si>
+    <t>Simple model</t>
+  </si>
+  <si>
+    <t>sc3</t>
+  </si>
+  <si>
+    <t>0 Bez zmeny politík</t>
+  </si>
+  <si>
+    <t>0 No policy change</t>
+  </si>
+  <si>
+    <t>ex17</t>
+  </si>
+  <si>
+    <t>Exportovať dáta</t>
+  </si>
+  <si>
+    <t>Export data</t>
+  </si>
+  <si>
     <t># Modelovanie zmien v poplatkoch za komunálny odpad
-    V tomto modeli je možné simulovať dopady zmien v oblasti zberu a poplatkov za komunálny odpad na výnos z poplatkov a náklady OLO. Zmenou rôznych vstupov, predpokladov a parametrov je možné modelovať očakávaný vývoj výnosov a nákladov v rôznych scenároch. Keďže množstvo dát z minulosti o reakcii obyvateľstva Bratislavy na zmeny v zbere odpadu, modelujeme viacere scenáre a ukazujeme tak rozsah možného vývoja. 
-    **Toto sú predpoklady, ktoré je možné meniť:**
-    1. Ročné tempo rastu výnosov z poplatku. Východisko je `1,5 %` ročne. Tento nárast vychádza z historického vývoja a reflektuje novú výstavbu a sťahovanie ľudí do mesta.
-    2. Podiel nádob v rodinných domoch, ktoré sú plné. Východisko je `53 %`. Toto vychádza z posledných výsledkov prieskumu o naplnenosti nádob. Táto hodnota má dopad na to, koľko ľudí v reakcii na zmenu poplatkov zmení veľkosť nádoby. 
-    3. Rozdiel v nákladoch OLO oproti zberným dvorom, prevádzkovaných mestskými časťami. Východisko je `1,5x`. Toto odráža fakt, že keď mestské časti prevádzkujú zberné dvory, volia si lacnejšie možnosti. 
-    4. Či má OLO prevziať odvoz odpadu z miestnych zberných dvorov. Ak áno, náklady na tento zvoz sú zahrnuté v nákladoch OLO. Môžete si vybrať medzi prevzatím zberných dvorov alebo aj zberných miest. 
-    5. Behaviorálne scenáre (viď nižšie). Celkové výsledky modelu ukazujú výsledky pre všetky tri scenáre. 
-    6. Východisková hodnota nákladov na ostatné aktivity spojené s nakladaním s odpadmi, ktoré sú hradené z poplatku, ale nie sú realizované OLO. 
-    7. Frekvencia zvozu kuchynského odpadu:
-    **Zvoz kuchynského odpadu:** 
-    Dnes sa kuchynský odpad zváža 2x týždenne medzi aprílom a novembrom. Počas zimy sa zváža 1x za týždeň.
-    Toto je možnosť `Súčaný stav`. Zmeniť je ju možné na: 
-    1. 2x/týždenne po celý rok. Toto zvýši počet zvozov z 87 na 104 a teda zvýši náklady približne o `19,5%`.
-    2. 1x/týždenne po celý rok. Toto zníži počet zvozov z 87 na 52 a teda zníži náklady približne o `40%`.
-    Dopad bude viditeľný na strane nákladov, v položke `1 OLO`.
+V tomto modeli je možné simulovať dopady zmien v oblasti zberu a poplatkov za komunálny odpad na výnos z poplatkov a náklady OLO. Zmenou rôznych vstupov, predpokladov a parametrov je možné modelovať očakávaný vývoj výnosov a nákladov v rôznych scenároch. Keďže množstvo dát z minulosti o reakcii obyvateľstva Bratislavy na zmeny v zbere odpadu, modelujeme viacere scenáre a ukazujeme tak rozsah možného vývoja. 
+**Toto sú predpoklady, ktoré je možné meniť:**
+1. Ročné tempo rastu výnosov z poplatku. Východisko je `1,5 %` ročne. Tento nárast vychádza z historického vývoja a reflektuje novú výstavbu a sťahovanie ľudí do mesta.
+2. Podiel nádob v rodinných domoch, ktoré sú plné. Východisko je `53 %`. Toto vychádza z posledných výsledkov prieskumu o naplnenosti nádob. Táto hodnota má dopad na to, koľko ľudí v reakcii na zmenu poplatkov zmení veľkosť nádoby. 
+3. Rozdiel v nákladoch OLO oproti zberným dvorom, prevádzkovaných mestskými časťami. Východisko je `1,5x`. Toto odráža fakt, že keď mestské časti prevádzkujú zberné dvory, volia si lacnejšie možnosti. 
+4. Či má OLO prevziať odvoz odpadu z miestnych zberných dvorov. Ak áno, náklady na tento zvoz sú zahrnuté v nákladoch OLO. Môžete si vybrať medzi prevzatím zberných dvorov alebo aj zberných miest. 
+5. Behaviorálne scenáre (viď nižšie). Celkové výsledky modelu ukazujú výsledky pre všetky tri scenáre. 
+6. Východisková hodnota nákladov na ostatné aktivity spojené s nakladaním s odpadmi, ktoré sú hradené z poplatku, ale nie sú realizované OLO. 
+7. Frekvencia zvozu kuchynského odpadu:
+**Zvoz kuchynského odpadu:** 
+Dnes sa kuchynský odpad zváža 2x týždenne medzi aprílom a novembrom. Počas zimy sa zváža 1x za týždeň.
+Toto je možnosť `Súčaný stav`. Zmeniť je ju možné na: 
+1. 2x/týždenne po celý rok. Toto zvýši počet zvozov z 87 na 104 a teda zvýši náklady približne o `19,5%`.
+2. 1x/týždenne po celý rok. Toto zníži počet zvozov z 87 na 52 a teda zníži náklady približne o `40%`.
+Dopad bude viditeľný na strane nákladov, v položke `1 OLO`.
 **Samotná simulácia dopadov sa nastavuje nasledovnými možnosťami:**
-    1. Zvýšenie sadzby poplatku (v %)
-    2. Zmena v možnostiach frekvencie zvozu
-    3. Počet obyvateľov na veľkú nádobu 1 100l
-    Taktiež je možné upraviť očakávané náklady OLO pre mesto, nahratím nového Excel súboru s aktualizovanými dátami. Výsledky sa automaticky aktualizujú. Excel súbor by mal obsahovať nasledovné hodnoty/štruktúru:
-    | Rok | 2024 | 2025 | 2026 | 2027 | 2028 | 2029 | 2030 |
-    |-----|------|------|------|------|------|------|------|
-    |NakladyOLO|
-    |Incineration|
-    |Residential waste collection|
-    |Green waste collection|
-    |Organic waste collection|
-    |Collection yards/points|
-    Simulácia sa nastavuje odlišne samostatne pre individuálnu bytovú výstavbu (rodinné domy) a samostatne pre bytové domy a podnikateľské subjekty. To je z toho dôvodu, že tieto skupiny reagujú odlišne na zmenu sadzieb. Zatiaľ čo pri IBV môžu občania meniť frekvenciu zvozu (štandardne majú len jednu nádobu), PO a bytové domy menia primárne počet nádob, zvozy sa upravujú iba v prípade, že nie je možné meniť počet nádob. 
-    Nastaviť môžete jednoduchý model (jednorazové zvýšenie poplatku v %) alebo komplexnejší krokový model, v ktorom je možné naplánovať viacero zmien v poplatkoch v čase.
-    ## Citlivostná analýza (zmena správania)
-    Štandardný model predpokladá zmenu správania v reakcií na zmenu v poplatkoch a iných podmienkach odvozu odpadu. Táto zmena je modelovaná na základe vývoja po ostatnej zmene sadzieb. Keďže sú však dáta relatívne obmedzené, pracujeme s viacerými scenármi behaviorálnych reakcií na zmeny politík.
-    Simulovať je možné nasledovné scenáre spreávania: 
-    1. **Bez zmeny správania**: Tento scenár nepredpokladá žiadne zmeny správania po zmene sadzieb. Jediná nevyhnutná zmena nastáva, keď je zrušená zmena týždenného zvozu v IBV. Toto spôsobí presun domácností na dvojtýždennu frekvenciu s väčšou nádobou (240l).
-    2. **Štandardná odozva**: Toto je východiskový scenár, ktorý z veľkej časti vychádza z extrapolácie toho, čo nastalo po ostatnej zmene poplatkov. Predpokladá relatívne miernu odozvu z hľadiska zmeny intervalov či počtu nádob. Avšak kapacita domácnosti znášať vyššie poplatky klesá s narastajúcimi poplatkami (aj v prípade rozdelenia zvýšenia do viacerých krokov).
-    3. **Výrazná odozva**: V tomto scenári predpokladáme, že oproti roku 2023 sa finančná situácia domácností zhoršila (kvôli inflácii a zvýšeniu iných daní). Reakcia na vyššie poplatky tak bude v tomto prípade výraznejšia.
-    Vo výsledkoch taktiež ukazujeme aj scenár **bez zmeny politík**. Teda scenár, kedy sa nezmenia ani sadzby, ani možné intervaly.</t>
+1. Zvýšenie sadzby poplatku (v %)
+2. Zmena v možnostiach frekvencie zvozu
+3. Počet obyvateľov na veľkú nádobu 1 100l
+Taktiež je možné upraviť očakávané náklady OLO pre mesto, nahratím nového Excel súboru s aktualizovanými dátami. Výsledky sa automaticky aktualizujú. Excel súbor by mal obsahovať nasledovné hodnoty/štruktúru:
+| Rok | 2024 | 2025 | 2026 | 2027 | 2028 | 2029 | 2030 |
+|-----|------|------|------|------|------|------|------|
+|NakladyOLO|
+|Incineration|
+|Residential waste collection|
+|Green waste collection|
+|Organic waste collection|
+|Collection yards/points|
+Simulácia sa nastavuje odlišne samostatne pre individuálnu bytovú výstavbu (rodinné domy) a samostatne pre bytové domy a podnikateľské subjekty. To je z toho dôvodu, že tieto skupiny reagujú odlišne na zmenu sadzieb. Zatiaľ čo pri IBV môžu občania meniť frekvenciu zvozu (štandardne majú len jednu nádobu), PO a bytové domy menia primárne počet nádob, zvozy sa upravujú iba v prípade, že nie je možné meniť počet nádob. 
+Nastaviť môžete jednoduchý model (jednorazové zvýšenie poplatku v %) alebo komplexnejší krokový model, v ktorom je možné naplánovať viacero zmien v poplatkoch v čase.
+## Citlivostná analýza (zmena správania)
+Štandardný model predpokladá zmenu správania v reakcií na zmenu v poplatkoch a iných podmienkach odvozu odpadu. Táto zmena je modelovaná na základe vývoja po ostatnej zmene sadzieb. Keďže sú však dáta relatívne obmedzené, pracujeme s viacerými scenármi behaviorálnych reakcií na zmeny politík.
+Simulovať je možné nasledovné scenáre spreávania: 
+1. **Bez zmeny správania**: Tento scenár nepredpokladá žiadne zmeny správania po zmene sadzieb. Jediná nevyhnutná zmena nastáva, keď je zrušená zmena týždenného zvozu v IBV. Toto spôsobí presun domácností na dvojtýždennu frekvenciu s väčšou nádobou (240l).
+2. **Štandardná odozva**: Toto je východiskový scenár, ktorý z veľkej časti vychádza z extrapolácie toho, čo nastalo po ostatnej zmene poplatkov. Predpokladá relatívne miernu odozvu z hľadiska zmeny intervalov či počtu nádob. Avšak kapacita domácnosti znášať vyššie poplatky klesá s narastajúcimi poplatkami (aj v prípade rozdelenia zvýšenia do viacerých krokov).
+3. **Výrazná odozva**: V tomto scenári predpokladáme, že oproti roku 2023 sa finančná situácia domácností zhoršila (kvôli inflácii a zvýšeniu iných daní). Reakcia na vyššie poplatky tak bude v tomto prípade výraznejšia.
+Vo výsledkoch taktiež ukazujeme aj scenár **bez zmeny politík**. Teda scenár, kedy sa nezmenia ani sadzby, ani možné intervaly.</t>
   </si>
   <si>
     <t># Simulation of PAYT reform
-    In this notebook we can simulate impacts of waste collection reforms on tax revenue and expenditures of OLO. 
-    We will adjust different parameters to show the expected evolution of key indicators in various scenarios. Since we have little available past data on how people in Bratislava respond to changes in waste collection, we need to model different scenarios to show a potential range of outcomes. 
-    **There are general assumptions you can setup:**
-    1. Annual rate of growth for fee collection. Default is `1.5%` per year. This represents new construction and more people moving in to the city.
-    2. Share of individual bins that are filled to capacity. Default is `53%`. This reflects latest results from a study of individual homes. This impacts how many people move to larger bins.
-    3. Assumption for how much more expensive OLO is compared to local yards. Default is `1.5x`. This reflects that when local districts handle waste, they usually choose cheaper options.
-    4. Whether OLO should take over local waste collection yards. If yes, the collection costs are added to costs of OLO. You can choose between taking over only proper collection yards or all collection points.
-    5. Behavioral scenario (see below). Total results show results for all scenarios.
-    6. Baseline value for other expenses covered by the waste fees.
-    7. Frequency of pickup of organic waste:
-    **Organic waste collection:** 
-    Currently organic waste is picked up 2x/week between April and November. During winter, this happens 1x/week. 
-    This is the `Default` option. You can change this to: 
-    1. 2x/week all year. This is assumed to increase the number of pickups from 87 to 104 and therefore increase costs by `~19.5%`.
-    2. 1x/week all year. This is assumed to decrease the number of pickups from 87 to 52 and therefore lower costs by `~40%`.
-    The impact will be shown on the expenditure side, in the `1 OLO` line item.
+In this notebook we can simulate impacts of waste collection reforms on tax revenue and expenditures of OLO. 
+We will adjust different parameters to show the expected evolution of key indicators in various scenarios. Since we have little available past data on how people in Bratislava respond to changes in waste collection, we need to model different scenarios to show a potential range of outcomes. 
+**There are general assumptions you can setup:**
+1. Annual rate of growth for fee collection. Default is `1.5%` per year. This represents new construction and more people moving in to the city.
+2. Share of individual bins that are filled to capacity. Default is `53%`. This reflects latest results from a study of individual homes. This impacts how many people move to larger bins.
+3. Assumption for how much more expensive OLO is compared to local yards. Default is `1.5x`. This reflects that when local districts handle waste, they usually choose cheaper options.
+4. Whether OLO should take over local waste collection yards. If yes, the collection costs are added to costs of OLO. You can choose between taking over only proper collection yards or all collection points.
+5. Behavioral scenario (see below). Total results show results for all scenarios.
+6. Baseline value for other expenses covered by the waste fees.
+7. Frequency of pickup of organic waste:
+**Organic waste collection:** 
+Currently organic waste is picked up 2x/week between April and November. During winter, this happens 1x/week. 
+This is the `Default` option. You can change this to: 
+1. 2x/week all year. This is assumed to increase the number of pickups from 87 to 104 and therefore increase costs by `~19.5%`.
+2. 1x/week all year. This is assumed to decrease the number of pickups from 87 to 52 and therefore lower costs by `~40%`.
+The impact will be shown on the expenditure side, in the `1 OLO` line item.
 **Here you can set up the simulation:**
-    1. Increase in fees (in %)
-    2. Removing / adding options of collection schedules
-    3. Number of people per large 1,100L bin
-    You can also adjust the assumed cost of OLO to the city by uploading a new Excel file with updated data. Upon changing the table, results will be automatically updated. The Excel file should contain the following values:
-    | Rok | 2024 | 2025 | 2026 | 2027 | 2028 | 2029 | 2030 |
-    |-----|------|------|------|------|------|------|------|
-    |NakladyOLO|
-    |Incineration|
-    |Residential waste collection|
-    |Green waste collection|
-    |Organic waste collection|
-    |Collection yards/points|
-    The simulation is parametrized differently for individual homes and differently for businesses/coops. This is because the assumption is that these groups respond differently to fee increases. While individual home owners can respond by frequency changes only (usually only have on bin), coops and businesses mostly adjust the number of bins, and only if this is not an option do they drop frequencies. 
-    You can setup a simple model (one % fee increase) or a stepped model where we can schedule several adjustments to fees over time.
-    ## Sensitivity settings (behavioral response)
-    The default model assumes a behavioral response to the changes in fees and other conditions that is most consistent with past trends. This data is very limited, and so we need to model different scenarios of how people might react to policy changes. 
-    You can choose these following scenarios to simulate:
-    1. **No behavioral change**: This scenario assumes no behavioral changes to an increase in fees. The only reaction that is required is when the weekly schedule is disabled. This will lead to a transfer of all households with a weekly schedule to a fortnightly schedule with the larger bin.
-    2. **Standard response**: This is the default scenario that mostly follows an extrapolation of what was observed after the last change to the fee structure. It assumes a fairly muted behavioral response to an increase in fees. However, the capacity of households to bear higher fees is assumed to fall with greater increases (even when you stagger them in multiple steps).
-    3. **Strong response**: This is a scenario where we assume that compared to 2023, the financial situation of households has worsened (following inflation and increases in other national taxes). Therefore the reaction to a higher waste fee will be more pronounced this time.
-    In the results, we also show a scenario of **No Policy Change**. That is, a scenario without changes to fees or other reforms that would affect revenues.</t>
-  </si>
-  <si>
-    <t>## Parameter setup</t>
-  </si>
-  <si>
-    <t>### General assumptions and policy changes</t>
-  </si>
-  <si>
-    <t>**Annual rate of growth for fee collection (new construction, etc.) in %**</t>
-  </si>
-  <si>
-    <t>**Make OLO handle waste collection from local waste collection yards**</t>
-  </si>
-  <si>
-    <t>**Share of individual bins that are filled to capacity in %**</t>
-  </si>
-  <si>
-    <t>**Behavioral scenario**</t>
-  </si>
-  <si>
-    <t>**Assumption for how much more expensive OLO is compared to local yards (multiplier)**</t>
-  </si>
-  <si>
-    <t>**2024 value for other expenses covered by waste fees**</t>
-  </si>
-  <si>
-    <t>**Organic waste pickup frequency**</t>
-  </si>
-  <si>
-    <t>**Upload new OLO expenditure**</t>
-  </si>
-  <si>
-    <t>### Individual homes (simple setup)</t>
-  </si>
-  <si>
-    <t>**1 Increase in standard fee in %**</t>
-  </si>
-  <si>
-    <t>**2 Force a maximum 14d interval for individual homes**</t>
-  </si>
-  <si>
-    <t>**3 Number of years to forecast**</t>
-  </si>
-  <si>
-    <t>### Individual homes (complex setup)</t>
-  </si>
-  <si>
-    <t>In this table, you can add multiple rows as steps in gradual fee increase / change</t>
-  </si>
-  <si>
-    <t>### Coops/businesses (simple setup)</t>
-  </si>
-  <si>
-    <t>**2 Number of people per 1110l bin**</t>
-  </si>
-  <si>
-    <t>### Coops/businesses (complex setup)</t>
-  </si>
-  <si>
-    <t>## Illustrations of monthly fee rises for current setup</t>
-  </si>
-  <si>
-    <t>### Household modelling</t>
-  </si>
-  <si>
-    <t>#### Simple setup</t>
-  </si>
-  <si>
-    <t>1 Individual home | Weekly pickup | 120L</t>
-  </si>
-  <si>
-    <t>€ monthly increase</t>
-  </si>
-  <si>
-    <t>2 Individual home | 2x monthly pickup | 120L</t>
-  </si>
-  <si>
-    <t>3 Block of flats | 2x weekly pickup | 1100L | 45 people per bin</t>
-  </si>
-  <si>
-    <t>4 Block of flats | 3x weekly pickup | 1100L | 60 people per bin</t>
-  </si>
-  <si>
-    <t>#### Stepped setup</t>
-  </si>
-  <si>
-    <t>### Per-bin modelling</t>
-  </si>
-  <si>
-    <t>5 120L | 2x monthly pickup</t>
-  </si>
-  <si>
-    <t>6 240L | 2x monthly pickup</t>
-  </si>
-  <si>
-    <t>7 1100L | 2x weekly pickup</t>
-  </si>
-  <si>
-    <t>## Total results for all behavioral scenarios</t>
-  </si>
-  <si>
-    <t>Total fee forecast per behavioral scenario (Simple | Organic Pickup:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total fee forecast per behavioral scenario (Stepped | Organic Pickup: </t>
-  </si>
-  <si>
-    <t>### Data from total results chart to export</t>
-  </si>
-  <si>
-    <t>You can press *Download* under the table to export your data to CSV to be used in Excel</t>
-  </si>
-  <si>
-    <t>Charts can be saved by clicking the ... button in the corner of the chart as an image</t>
-  </si>
-  <si>
-    <t>## Simulation results (Fees)</t>
-  </si>
-  <si>
-    <t>Below you can see the total results for the current simulation setup for fees in EUR.</t>
-  </si>
-  <si>
-    <t>The table shows fees before change implementation, first year after implementation and in the last projected period.</t>
-  </si>
-  <si>
-    <t>Then the following charts show a detailed evolution over time of fee collection and the number of bins.</t>
-  </si>
-  <si>
-    <t>## Parametre modelu</t>
-  </si>
-  <si>
-    <t>### Všeobecné predpoklady a zmeny politík</t>
-  </si>
-  <si>
-    <t>**Ročné tempo rastu výnosov z poplatku (nová výstavba, atď.) v %**</t>
-  </si>
-  <si>
-    <t>**Prevezme OLO odvoz odpadu z miestnych zberných dvorov?**</t>
-  </si>
-  <si>
-    <t>**Podiel individuálnych nádob, ktoré sú plné, v %**</t>
-  </si>
-  <si>
-    <t>**Scenáre správania**</t>
-  </si>
-  <si>
-    <t>**Predpoklad rozdielu v nákladoch medzi OLO a miestnych zberných dvorov (násobok)**</t>
-  </si>
-  <si>
-    <t>**Hodnota pre ostatné náklady, hradené z poplatku (pre rok 2024)**</t>
-  </si>
-  <si>
-    <t>**Frekvencia zvozu kuchynského odpadu**</t>
-  </si>
-  <si>
-    <t>**Nahrať nové náklady OLO**</t>
-  </si>
-  <si>
-    <t>### IBV (jednoduchý model)</t>
-  </si>
-  <si>
-    <t>**1 Zvýšenie základného poplatku o %**</t>
-  </si>
-  <si>
-    <t>**2 Maximálna frekvencia 2x mesiac**</t>
-  </si>
-  <si>
-    <t>**3 Počet rokov prognózy**</t>
-  </si>
-  <si>
-    <t>### IBV (komplexný model)</t>
-  </si>
-  <si>
-    <t>V tejto tabuľke môžete pridávať riadky ako kroky v postupných zmenách poplatkov</t>
-  </si>
-  <si>
-    <t>### BD a PO (jednoduchý model)</t>
-  </si>
-  <si>
-    <t>**2 Počet obyvateľov na 1 110l nádobu**</t>
-  </si>
-  <si>
-    <t>### BD a PO (komplexný model)</t>
-  </si>
-  <si>
-    <t>## Príklady mesačných nárastov poplatok pre aktuálne nastavený model</t>
-  </si>
-  <si>
-    <t>### Domácnosti</t>
-  </si>
-  <si>
-    <t>#### Jednoduchý model</t>
-  </si>
-  <si>
-    <t>1 IBV | Týždenný zvoz | 120l</t>
-  </si>
-  <si>
-    <t>€ mesačný nárast</t>
-  </si>
-  <si>
-    <t>2 IBV | Zvoz 2x mesačne | 120l</t>
-  </si>
-  <si>
-    <t>3 Bytové domy | Zvoz 2x týždenne | 1100l | 45 ľudí na nádobu | 2 ľudia na domácnosť</t>
-  </si>
-  <si>
-    <t>4 Bytové domy | Zvoz 3x týždenne | 1100l | 60 ľudí na nádobu | 2 ľudia na domácnosť</t>
-  </si>
-  <si>
-    <t>#### Komplexný model</t>
-  </si>
-  <si>
-    <t>### Nádoby</t>
-  </si>
-  <si>
-    <t>5 120l | Zvoz 2x mesačne</t>
-  </si>
-  <si>
-    <t>6 240l | Zvoz 2x mesačne</t>
-  </si>
-  <si>
-    <t>7 1100l | Zvoz 2x týždenne</t>
-  </si>
-  <si>
-    <t>Celkový odhad výnosov z poplatku pre každý scenár (Jednoduchý model | Kuchynský odpad:</t>
-  </si>
-  <si>
-    <t>Celkový odhad výnosov z poplatku pre každý scenár (Komplexný model | Kuchynský odpad:</t>
-  </si>
-  <si>
-    <t>## Celkový výsledky pre všetky scenáre správania</t>
-  </si>
-  <si>
-    <t>### Dáta z grafu na export</t>
-  </si>
-  <si>
-    <t>Stlačením tlačidla *Download* pod tabuľkou exportujete dáta do CSV formátu, ktorý je možné použiť v Exceli</t>
-  </si>
-  <si>
-    <t>Grafy môžu byť uložené stlačením tlačidla ... v rohu grafu ako obrázok</t>
-  </si>
-  <si>
-    <t>Exportované dáta obsahujú aj zhrnutie použitých predpokladov</t>
-  </si>
-  <si>
-    <t>Exported data contain a summary of used assumptions</t>
-  </si>
-  <si>
-    <t>## Výsledky simulácie (výnos z poplatku)</t>
-  </si>
-  <si>
-    <t>Nižšie môžete vidieť celkové výsledky pre aktuálne nastavenie modelu pre výnosy z poplatku v EUR.</t>
-  </si>
-  <si>
-    <t>Tabuľka ukazuje výnosy pred zmenu, prvý rok po zmene a v poslednom roku prognózovaného obdobia.</t>
-  </si>
-  <si>
-    <t>Následne, detailné grafy ukazujú vývoj výnosov a počtu nádob v čase.</t>
-  </si>
-  <si>
-    <t>p1</t>
-  </si>
-  <si>
-    <t>p2</t>
-  </si>
-  <si>
-    <t>p3</t>
-  </si>
-  <si>
-    <t>p4</t>
-  </si>
-  <si>
-    <t>p5</t>
-  </si>
-  <si>
-    <t>p6</t>
-  </si>
-  <si>
-    <t>p7</t>
-  </si>
-  <si>
-    <t>p8</t>
-  </si>
-  <si>
-    <t>p9</t>
-  </si>
-  <si>
-    <t>p10</t>
-  </si>
-  <si>
-    <t>s1</t>
-  </si>
-  <si>
-    <t>s2</t>
-  </si>
-  <si>
-    <t>s3</t>
-  </si>
-  <si>
-    <t>s4</t>
-  </si>
-  <si>
-    <t>s5</t>
-  </si>
-  <si>
-    <t>s6</t>
-  </si>
-  <si>
-    <t>s7</t>
-  </si>
-  <si>
-    <t>s8</t>
-  </si>
-  <si>
-    <t>s9</t>
-  </si>
-  <si>
-    <t>s10</t>
-  </si>
-  <si>
-    <t>s11</t>
-  </si>
-  <si>
-    <t>e1</t>
-  </si>
-  <si>
-    <t>e2</t>
-  </si>
-  <si>
-    <t>e3</t>
-  </si>
-  <si>
-    <t>e4</t>
-  </si>
-  <si>
-    <t>e5</t>
-  </si>
-  <si>
-    <t>e6</t>
-  </si>
-  <si>
-    <t>e7</t>
-  </si>
-  <si>
-    <t>e8</t>
-  </si>
-  <si>
-    <t>e9</t>
-  </si>
-  <si>
-    <t>e10</t>
-  </si>
-  <si>
-    <t>e11</t>
-  </si>
-  <si>
-    <t>e12</t>
-  </si>
-  <si>
-    <t>e13</t>
-  </si>
-  <si>
-    <t>l1</t>
-  </si>
-  <si>
-    <t>l2</t>
-  </si>
-  <si>
-    <t>r1</t>
-  </si>
-  <si>
-    <t>r2</t>
-  </si>
-  <si>
-    <t>r3</t>
-  </si>
-  <si>
-    <t>r4</t>
-  </si>
-  <si>
-    <t>r5</t>
-  </si>
-  <si>
-    <t>r6</t>
-  </si>
-  <si>
-    <t>r7</t>
-  </si>
-  <si>
-    <t>r8</t>
-  </si>
-  <si>
-    <t>r9</t>
+1. Increase in fees (in %)
+2. Removing / adding options of collection schedules
+3. Number of people per large 1,100L bin
+You can also adjust the assumed cost of OLO to the city by uploading a new Excel file with updated data. Upon changing the table, results will be automatically updated. The Excel file should contain the following values:
+| Rok | 2024 | 2025 | 2026 | 2027 | 2028 | 2029 | 2030 |
+|-----|------|------|------|------|------|------|------|
+|NakladyOLO|
+|Incineration|
+|Residential waste collection|
+|Green waste collection|
+|Organic waste collection|
+|Collection yards/points|
+The simulation is parametrized differently for individual homes and differently for businesses/coops. This is because the assumption is that these groups respond differently to fee increases. While individual home owners can respond by frequency changes only (usually only have on bin), coops and businesses mostly adjust the number of bins, and only if this is not an option do they drop frequencies. 
+You can setup a simple model (one % fee increase) or a stepped model where we can schedule several adjustments to fees over time.
+## Sensitivity settings (behavioral response)
+The default model assumes a behavioral response to the changes in fees and other conditions that is most consistent with past trends. This data is very limited, and so we need to model different scenarios of how people might react to policy changes. 
+You can choose these following scenarios to simulate:
+1. **No behavioral change**: This scenario assumes no behavioral changes to an increase in fees. The only reaction that is required is when the weekly schedule is disabled. This will lead to a transfer of all households with a weekly schedule to a fortnightly schedule with the larger bin.
+2. **Standard response**: This is the default scenario that mostly follows an extrapolation of what was observed after the last change to the fee structure. It assumes a fairly muted behavioral response to an increase in fees. However, the capacity of households to bear higher fees is assumed to fall with greater increases (even when you stagger them in multiple steps).
+3. **Strong response**: This is a scenario where we assume that compared to 2023, the financial situation of households has worsened (following inflation and increases in other national taxes). Therefore the reaction to a higher waste fee will be more pronounced this time.
+In the results, we also show a scenario of **No Policy Change**. That is, a scenario without changes to fees or other reforms that would affect revenues.</t>
   </si>
 </sst>
 </file>
@@ -909,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F81EA9-A9C7-6E4A-8243-CC330D585D50}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="93.83203125" customWidth="1"/>
@@ -932,505 +1193,824 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>222</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C47" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>135</v>
+      </c>
+      <c r="B57" t="s">
         <v>136</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" t="s">
-        <v>47</v>
+      <c r="C57" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>147</v>
+      </c>
+      <c r="B61" t="s">
+        <v>148</v>
+      </c>
+      <c r="C61" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>150</v>
+      </c>
+      <c r="B62" t="s">
+        <v>151</v>
+      </c>
+      <c r="C62" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>153</v>
+      </c>
+      <c r="B63" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B65" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" t="s">
+        <v>162</v>
+      </c>
+      <c r="C66" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>171</v>
+      </c>
+      <c r="B67" t="s">
+        <v>165</v>
+      </c>
+      <c r="C67" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>172</v>
+      </c>
+      <c r="B68" t="s">
+        <v>166</v>
+      </c>
+      <c r="C68" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>173</v>
+      </c>
+      <c r="B69" t="s">
+        <v>167</v>
+      </c>
+      <c r="C69" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>174</v>
+      </c>
+      <c r="B70" t="s">
+        <v>168</v>
+      </c>
+      <c r="C70" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>175</v>
+      </c>
+      <c r="B71" t="s">
+        <v>169</v>
+      </c>
+      <c r="C71" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>176</v>
+      </c>
+      <c r="B72" t="s">
+        <v>170</v>
+      </c>
+      <c r="C72" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>219</v>
+      </c>
+      <c r="B73" t="s">
+        <v>220</v>
+      </c>
+      <c r="C73" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>183</v>
+      </c>
+      <c r="B74" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>193</v>
+      </c>
+      <c r="B75" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>194</v>
+      </c>
+      <c r="B76" t="s">
+        <v>186</v>
+      </c>
+      <c r="C76" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>195</v>
+      </c>
+      <c r="B77" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>196</v>
+      </c>
+      <c r="B78" t="s">
+        <v>188</v>
+      </c>
+      <c r="C78" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>197</v>
+      </c>
+      <c r="B79" t="s">
+        <v>189</v>
+      </c>
+      <c r="C79" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>198</v>
+      </c>
+      <c r="B80" t="s">
+        <v>190</v>
+      </c>
+      <c r="C80" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>199</v>
+      </c>
+      <c r="B81" t="s">
+        <v>191</v>
+      </c>
+      <c r="C81" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>200</v>
+      </c>
+      <c r="B82" t="s">
+        <v>192</v>
+      </c>
+      <c r="C82" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>210</v>
+      </c>
+      <c r="B84" t="s">
+        <v>211</v>
+      </c>
+      <c r="C84" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>213</v>
+      </c>
+      <c r="B85" t="s">
+        <v>214</v>
+      </c>
+      <c r="C85" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>216</v>
+      </c>
+      <c r="B86" t="s">
+        <v>217</v>
+      </c>
+      <c r="C86" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/public/translation.xlsx
+++ b/public/translation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2293b72959587e28/PAYT_ANALYSIS/model/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="8_{6AF8692F-890D-1B44-9F64-197BE6160813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E71E475-E12D-8E4F-BAC4-DC8AE45E9391}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="8_{6AF8692F-890D-1B44-9F64-197BE6160813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0CD88BF-FB12-A441-A664-6BB3FA9333E7}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="12540" windowWidth="31520" windowHeight="14460" xr2:uid="{8B6CA0FD-2112-BC45-8C8C-A886CDF59FA5}"/>
+    <workbookView xWindow="240" yWindow="600" windowWidth="31520" windowHeight="26400" xr2:uid="{8B6CA0FD-2112-BC45-8C8C-A886CDF59FA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="287">
   <si>
     <t>key</t>
   </si>
@@ -783,6 +783,195 @@
 2. **Standard response**: This is the default scenario that mostly follows an extrapolation of what was observed after the last change to the fee structure. It assumes a fairly muted behavioral response to an increase in fees. However, the capacity of households to bear higher fees is assumed to fall with greater increases (even when you stagger them in multiple steps).
 3. **Strong response**: This is a scenario where we assume that compared to 2023, the financial situation of households has worsened (following inflation and increases in other national taxes). Therefore the reaction to a higher waste fee will be more pronounced this time.
 In the results, we also show a scenario of **No Policy Change**. That is, a scenario without changes to fees or other reforms that would affect revenues.</t>
+  </si>
+  <si>
+    <t>t1</t>
+  </si>
+  <si>
+    <t>Nárast poplatku v %</t>
+  </si>
+  <si>
+    <t>Fee increase in %</t>
+  </si>
+  <si>
+    <t>Odstup v rokoch</t>
+  </si>
+  <si>
+    <t>Gap in years</t>
+  </si>
+  <si>
+    <t>t2</t>
+  </si>
+  <si>
+    <t>t3</t>
+  </si>
+  <si>
+    <t>Maximálne 14d interval</t>
+  </si>
+  <si>
+    <t>Disable weekly pickup</t>
+  </si>
+  <si>
+    <t>Počet ľudí na nádobu</t>
+  </si>
+  <si>
+    <t>People per bin</t>
+  </si>
+  <si>
+    <t>t4</t>
+  </si>
+  <si>
+    <t>cr1</t>
+  </si>
+  <si>
+    <t>Coop fees</t>
+  </si>
+  <si>
+    <t>Výnosy (BD)</t>
+  </si>
+  <si>
+    <t>cr2</t>
+  </si>
+  <si>
+    <t>Coop bin count</t>
+  </si>
+  <si>
+    <t>Počet nádob (BD)</t>
+  </si>
+  <si>
+    <t>gr1</t>
+  </si>
+  <si>
+    <t>Rok</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>gr2</t>
+  </si>
+  <si>
+    <t>Scenár</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>sc0</t>
+  </si>
+  <si>
+    <t>cr3</t>
+  </si>
+  <si>
+    <t>Vývoj výnosov od bytových domov a PO v EUR</t>
+  </si>
+  <si>
+    <t>Revenue from coops and businesses in EUR</t>
+  </si>
+  <si>
+    <t>cr4</t>
+  </si>
+  <si>
+    <t>Number of bins with coops and businesses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vývoj počtu nádob v bytových domoch a PO </t>
+  </si>
+  <si>
+    <t>gr3</t>
+  </si>
+  <si>
+    <t>Platiteľ</t>
+  </si>
+  <si>
+    <t>Payee</t>
+  </si>
+  <si>
+    <t>gr4</t>
+  </si>
+  <si>
+    <t>0: Pred zmenou</t>
+  </si>
+  <si>
+    <t>0: Before change</t>
+  </si>
+  <si>
+    <t>gr5</t>
+  </si>
+  <si>
+    <t>1: Prvý rok po zmene</t>
+  </si>
+  <si>
+    <t>1: First year after change</t>
+  </si>
+  <si>
+    <t>gr6</t>
+  </si>
+  <si>
+    <t>IBV</t>
+  </si>
+  <si>
+    <t>Individual households</t>
+  </si>
+  <si>
+    <t>gr7</t>
+  </si>
+  <si>
+    <t>BD a PO</t>
+  </si>
+  <si>
+    <t>Coops and businesses</t>
+  </si>
+  <si>
+    <t>2: Posledné prognóznované obdobie</t>
+  </si>
+  <si>
+    <t>gr8</t>
+  </si>
+  <si>
+    <t>2: Last forecast period</t>
+  </si>
+  <si>
+    <t>gr9</t>
+  </si>
+  <si>
+    <t>Spolu</t>
+  </si>
+  <si>
+    <t>Together</t>
+  </si>
+  <si>
+    <t>gr10</t>
+  </si>
+  <si>
+    <t>Výnos z poplatku</t>
+  </si>
+  <si>
+    <t>Fee forecast</t>
+  </si>
+  <si>
+    <t>ir1</t>
+  </si>
+  <si>
+    <t>Vývoj výnosov z IBV v EUR</t>
+  </si>
+  <si>
+    <t>Revenue from individual homes in EUR</t>
+  </si>
+  <si>
+    <t>ir2</t>
+  </si>
+  <si>
+    <t>gr11</t>
+  </si>
+  <si>
+    <t>Počet nádob</t>
+  </si>
+  <si>
+    <t>Bin count</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F81EA9-A9C7-6E4A-8243-CC330D585D50}">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="93.83203125" customWidth="1"/>
@@ -1980,6 +2169,17 @@
         <v>209</v>
       </c>
     </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>249</v>
+      </c>
+      <c r="B83" t="s">
+        <v>246</v>
+      </c>
+      <c r="C83" t="s">
+        <v>247</v>
+      </c>
+    </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>210</v>
@@ -2011,6 +2211,231 @@
       </c>
       <c r="C86" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>224</v>
+      </c>
+      <c r="B88" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>229</v>
+      </c>
+      <c r="B89" t="s">
+        <v>227</v>
+      </c>
+      <c r="C89" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>230</v>
+      </c>
+      <c r="B90" t="s">
+        <v>231</v>
+      </c>
+      <c r="C90" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>235</v>
+      </c>
+      <c r="B91" t="s">
+        <v>233</v>
+      </c>
+      <c r="C91" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>236</v>
+      </c>
+      <c r="B93" t="s">
+        <v>238</v>
+      </c>
+      <c r="C93" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>239</v>
+      </c>
+      <c r="B94" t="s">
+        <v>241</v>
+      </c>
+      <c r="C94" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>250</v>
+      </c>
+      <c r="B95" t="s">
+        <v>251</v>
+      </c>
+      <c r="C95" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>253</v>
+      </c>
+      <c r="B96" t="s">
+        <v>255</v>
+      </c>
+      <c r="C96" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>242</v>
+      </c>
+      <c r="B97" t="s">
+        <v>243</v>
+      </c>
+      <c r="C97" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>245</v>
+      </c>
+      <c r="B98" t="s">
+        <v>248</v>
+      </c>
+      <c r="C98" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>256</v>
+      </c>
+      <c r="B99" t="s">
+        <v>257</v>
+      </c>
+      <c r="C99" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>259</v>
+      </c>
+      <c r="B100" t="s">
+        <v>260</v>
+      </c>
+      <c r="C100" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>262</v>
+      </c>
+      <c r="B101" t="s">
+        <v>263</v>
+      </c>
+      <c r="C101" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>265</v>
+      </c>
+      <c r="B102" t="s">
+        <v>266</v>
+      </c>
+      <c r="C102" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>268</v>
+      </c>
+      <c r="B103" t="s">
+        <v>269</v>
+      </c>
+      <c r="C103" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>272</v>
+      </c>
+      <c r="B104" t="s">
+        <v>271</v>
+      </c>
+      <c r="C104" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>274</v>
+      </c>
+      <c r="B105" t="s">
+        <v>275</v>
+      </c>
+      <c r="C105" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>277</v>
+      </c>
+      <c r="B106" t="s">
+        <v>278</v>
+      </c>
+      <c r="C106" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>284</v>
+      </c>
+      <c r="B107" t="s">
+        <v>285</v>
+      </c>
+      <c r="C107" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>280</v>
+      </c>
+      <c r="B108" t="s">
+        <v>281</v>
+      </c>
+      <c r="C108" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/public/translation.xlsx
+++ b/public/translation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2293b72959587e28/PAYT_ANALYSIS/model/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="8_{6AF8692F-890D-1B44-9F64-197BE6160813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0CD88BF-FB12-A441-A664-6BB3FA9333E7}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="8_{6AF8692F-890D-1B44-9F64-197BE6160813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27BD6503-F2E8-C244-AD0A-18F8313AFDF6}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="600" windowWidth="31520" windowHeight="26400" xr2:uid="{8B6CA0FD-2112-BC45-8C8C-A886CDF59FA5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="301">
   <si>
     <t>key</t>
   </si>
@@ -962,9 +962,6 @@
     <t>Revenue from individual homes in EUR</t>
   </si>
   <si>
-    <t>ir2</t>
-  </si>
-  <si>
     <t>gr11</t>
   </si>
   <si>
@@ -972,6 +969,51 @@
   </si>
   <si>
     <t>Bin count</t>
+  </si>
+  <si>
+    <t>olo1</t>
+  </si>
+  <si>
+    <t>2 Ostatné náklady</t>
+  </si>
+  <si>
+    <t>2 Other expenses</t>
+  </si>
+  <si>
+    <t>olo2</t>
+  </si>
+  <si>
+    <t>4 OLO Zberné dvory</t>
+  </si>
+  <si>
+    <t>4 OLO Waste yards</t>
+  </si>
+  <si>
+    <t>olo3</t>
+  </si>
+  <si>
+    <t>3 Podiel MČ</t>
+  </si>
+  <si>
+    <t>3 City district share</t>
+  </si>
+  <si>
+    <t>olo4</t>
+  </si>
+  <si>
+    <t>Kategória</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>olo5</t>
+  </si>
+  <si>
+    <t>Náklady</t>
+  </si>
+  <si>
+    <t>Expenses</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F81EA9-A9C7-6E4A-8243-CC330D585D50}">
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="93.83203125" customWidth="1"/>
@@ -2413,13 +2455,13 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
+        <v>283</v>
+      </c>
+      <c r="B107" t="s">
         <v>284</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
         <v>285</v>
-      </c>
-      <c r="C107" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -2433,9 +2475,59 @@
         <v>282</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>283</v>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>286</v>
+      </c>
+      <c r="B110" t="s">
+        <v>287</v>
+      </c>
+      <c r="C110" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>289</v>
+      </c>
+      <c r="B111" t="s">
+        <v>290</v>
+      </c>
+      <c r="C111" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>292</v>
+      </c>
+      <c r="B112" t="s">
+        <v>293</v>
+      </c>
+      <c r="C112" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>295</v>
+      </c>
+      <c r="B113" t="s">
+        <v>296</v>
+      </c>
+      <c r="C113" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>298</v>
+      </c>
+      <c r="B114" t="s">
+        <v>299</v>
+      </c>
+      <c r="C114" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
